--- a/Experiment analysis results/Additional file 1.xlsx
+++ b/Experiment analysis results/Additional file 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71748646-B055-4E23-9042-038D3D9A668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C20D76-FDC8-489B-B99A-DA5450C74BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,13 +117,13 @@
     <t>#Reference cells</t>
   </si>
   <si>
-    <t>Cell types</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
     <t>#CARD_SCMapping-inferred cells</t>
+  </si>
+  <si>
+    <t>Cell-type abundance</t>
   </si>
 </sst>
 </file>
@@ -526,13 +526,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -639,22 +639,22 @@
         <v>403.69281101067099</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -699,22 +699,22 @@
         <v>86.766287271465899</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -759,22 +759,22 @@
         <v>640.11817199627899</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -815,10 +815,10 @@
         <v>461.274710727539</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O6" s="4">
         <v>494.48644211849899</v>
@@ -830,13 +830,13 @@
         <v>503.33749637788702</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -875,10 +875,10 @@
         <v>484.83238806803598</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O7" s="4">
         <v>28.680345407271901</v>
@@ -890,13 +890,13 @@
         <v>774.99537068471295</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
         <v>1.18949009064092</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="4">
         <v>2525.3795100925699</v>
@@ -935,10 +935,10 @@
         <v>171.16197909678201</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="4">
         <v>355.27791945135198</v>
@@ -950,13 +950,13 @@
         <v>10.726210227615301</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -988,7 +988,7 @@
         <v>599.41358549207996</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K9" s="5">
         <v>151.061798839495</v>
@@ -1003,13 +1003,13 @@
         <v>78.018753414855794</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P9" s="5">
         <v>0.89199007763166704</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R9" s="5">
         <v>1320.55984579868</v>
@@ -1048,7 +1048,7 @@
         <v>912.57910180796</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="5">
         <v>370.16596174420602</v>
@@ -1063,13 +1063,13 @@
         <v>444.35290494194101</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P10" s="5">
         <v>27.320912527988899</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R10" s="5">
         <v>438.13590183694703</v>
@@ -1105,10 +1105,10 @@
         <v>2.0217208693814701</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K11" s="5">
         <v>879.38720684782504</v>
@@ -1120,16 +1120,16 @@
         <v>66.590769396496896</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" s="5">
         <v>34.793119930923403</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R11" s="5">
         <v>288.67069479922401</v>
@@ -1138,7 +1138,7 @@
         <v>627.58439874330998</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -1173,7 +1173,7 @@
         <v>0.19008857958604</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L12" s="4">
         <v>71.837275239851394</v>
@@ -1182,19 +1182,19 @@
         <v>661.55329727275398</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P12" s="4">
         <v>3.3881372490130901</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S12" s="4">
         <v>1388.49457249429</v>
@@ -1233,7 +1233,7 @@
         <v>1.6678188788127299</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L13" s="4">
         <v>268.80715851631902</v>
@@ -1242,19 +1242,19 @@
         <v>2459.9356316776498</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P13" s="4">
         <v>32.477232009721298</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S13" s="4">
         <v>40.082445011028902</v>
@@ -1293,7 +1293,7 @@
         <v>24.718265331062899</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L14" s="4">
         <v>1375.2279621226201</v>
@@ -1302,19 +1302,19 @@
         <v>33.369482856564701</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P14" s="4">
         <v>65.864821616261196</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S14" s="4">
         <v>1302.39138058709</v>
